--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_24.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_24.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Smoker?</t>
+          <t>Musician?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Response</t>
+          <t>Anxiety</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.262827766056597</v>
+        <v>0.2509227119933199</v>
       </c>
       <c r="C2">
-        <v>0.05700562636623011</v>
+        <v>0.5851223253319913</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3824549196577713</v>
+        <v>-0.5304352995925737</v>
       </c>
       <c r="C3">
-        <v>-0.2154403713659655</v>
+        <v>-0.2330926759163897</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.3617970769432</v>
+        <v>0.1674231262993648</v>
       </c>
       <c r="C4">
-        <v>-0.4301846300507689</v>
+        <v>-0.7670553869816494</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.6106922084318641</v>
+        <v>0.1092609649308171</v>
       </c>
       <c r="C5">
-        <v>-0.5201984463949163</v>
+        <v>0.1780986716481767</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.6326646434754695</v>
+        <v>-0.1403454682843069</v>
       </c>
       <c r="C6">
-        <v>-0.5377828966692826</v>
+        <v>-0.3583344701275055</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.3392433481542139</v>
+        <v>1.667274261202309</v>
       </c>
       <c r="C7">
-        <v>-0.7383161789713021</v>
+        <v>0.3275254713162865</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-1.259157448108824</v>
+        <v>-0.08891114870364984</v>
       </c>
       <c r="C8">
-        <v>0.9847021194610516</v>
+        <v>1.563822498923756</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-1.557221148523768</v>
+        <v>0.4357279657975267</v>
       </c>
       <c r="C9">
-        <v>-0.0625741028559762</v>
+        <v>0.20022508854844</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.008981308205997927</v>
+        <v>-0.3603364025307276</v>
       </c>
       <c r="C10">
-        <v>-0.89176952217779</v>
+        <v>0.5534523330672616</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.8029107871610153</v>
+        <v>-0.7986400370213248</v>
       </c>
       <c r="C11">
-        <v>-2.893944878608568</v>
+        <v>0.5364935132133349</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>1.369161410860374</v>
+        <v>0.3655803910018141</v>
       </c>
       <c r="C12">
-        <v>-0.04749247479807451</v>
+        <v>0.9226122627958566</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.3379234323318101</v>
+        <v>1.493349338469342</v>
       </c>
       <c r="C13">
-        <v>-0.4513379947454307</v>
+        <v>-0.8725732415713794</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-1.673369824196255</v>
+        <v>0.2291977826255967</v>
       </c>
       <c r="C14">
-        <v>-1.125892821837337</v>
+        <v>-1.047154719927185</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.2082518307804847</v>
+        <v>0.5940570603168994</v>
       </c>
       <c r="C15">
-        <v>-1.606429302912834</v>
+        <v>-1.131863563483914</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.4910621743070349</v>
+        <v>2.382186599677484</v>
       </c>
       <c r="C16">
-        <v>1.063068652703545</v>
+        <v>-1.387421350781353</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.2907504587143336</v>
+        <v>-0.1621607166552901</v>
       </c>
       <c r="C17">
-        <v>-0.069957503758211</v>
+        <v>0.330356955270462</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.2125125465436602</v>
+        <v>-0.7782995881426076</v>
       </c>
       <c r="C18">
-        <v>1.844082486762058</v>
+        <v>-0.01127075867439981</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.1054766037444779</v>
+        <v>0.7256974063665208</v>
       </c>
       <c r="C19">
-        <v>-0.09671259674069264</v>
+        <v>-0.8070561464809241</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.7096751591928304</v>
+        <v>-0.07973986603897119</v>
       </c>
       <c r="C20">
-        <v>-0.1941170959050506</v>
+        <v>0.3642651840774914</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.277217481318621</v>
+        <v>-1.25971120159825</v>
       </c>
       <c r="C21">
-        <v>-0.1687540652404472</v>
+        <v>1.627467422837539</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.01243465574407284</v>
+        <v>-0.8945507947704129</v>
       </c>
       <c r="C22">
-        <v>-1.520686402287232</v>
+        <v>0.7745518408968153</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.055578131828617</v>
+        <v>1.389429299825954</v>
       </c>
       <c r="C23">
-        <v>1.345372961231798</v>
+        <v>0.5550582225664924</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.4065637496129525</v>
+        <v>1.121312110137471</v>
       </c>
       <c r="C24">
-        <v>-0.4193158306723176</v>
+        <v>-1.902222830698774</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.050185629719275</v>
+        <v>-0.526308344551997</v>
       </c>
       <c r="C25">
-        <v>-0.1361973474655118</v>
+        <v>1.088018615742673</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.701550658619804</v>
+        <v>-0.1458424179190917</v>
       </c>
       <c r="C26">
-        <v>-1.088511760696472</v>
+        <v>0.407155008483623</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.431038275768655</v>
+        <v>-0.3558773265608017</v>
       </c>
       <c r="C27">
-        <v>-0.5118203799216449</v>
+        <v>-0.2993572508154745</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.90075609163404</v>
+        <v>0.4532008706809299</v>
       </c>
       <c r="C28">
-        <v>-1.077740005371385</v>
+        <v>-1.206767984889806</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.5388066080468228</v>
+        <v>1.079622332366442</v>
       </c>
       <c r="C29">
-        <v>0.415267015308876</v>
+        <v>-1.641865346244204</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.6055171006892818</v>
+        <v>-0.03155343350970646</v>
       </c>
       <c r="C30">
-        <v>0.275994439634366</v>
+        <v>0.8186951427962327</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-1.584585877148839</v>
+        <v>0.765095583984964</v>
       </c>
       <c r="C31">
-        <v>-0.2697190623543795</v>
+        <v>1.297169138573344</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.433865350327534</v>
+        <v>1.091081017694993</v>
       </c>
       <c r="C32">
-        <v>-0.4588129623959402</v>
+        <v>-0.5120379693649276</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.7237611785309451</v>
+        <v>0.2699727383192348</v>
       </c>
       <c r="C33">
-        <v>0.6359891387929549</v>
+        <v>0.5194366316367383</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-1.370863280500293</v>
+        <v>-0.3725206845724848</v>
       </c>
       <c r="C34">
-        <v>-0.01457712856869537</v>
+        <v>-1.169090822140979</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.418761287411108</v>
+        <v>1.873445151314827</v>
       </c>
       <c r="C35">
-        <v>0.1131866136192814</v>
+        <v>-0.1382665176094229</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.1486133212955165</v>
+        <v>1.708402304033124</v>
       </c>
       <c r="C36">
-        <v>-0.1604230888391029</v>
+        <v>-0.7858824330590104</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.146186904897626</v>
+        <v>-0.5253712255298265</v>
       </c>
       <c r="C37">
-        <v>0.2568450864289579</v>
+        <v>2.254449205796937</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.5362131089814697</v>
+        <v>1.563824045996658</v>
       </c>
       <c r="C38">
-        <v>0.143532909275723</v>
+        <v>-0.458936420743524</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.002071893328470331</v>
+        <v>0.5196477889517914</v>
       </c>
       <c r="C39">
-        <v>-0.1075185550862757</v>
+        <v>-0.1045503565958029</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.171989808952631</v>
+        <v>-0.237371296728427</v>
       </c>
       <c r="C40">
-        <v>-0.5472244553790254</v>
+        <v>-0.8152314416671677</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.883557588264671</v>
+        <v>-0.1616613885103741</v>
       </c>
       <c r="C41">
-        <v>1.16212977625863</v>
+        <v>-1.437601534207782</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.9097038114463669</v>
+        <v>-0.9636681007457458</v>
       </c>
       <c r="C42">
-        <v>-0.1238239330905737</v>
+        <v>1.918444904982685</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.2187204186155162</v>
+        <v>0.3053447641517276</v>
       </c>
       <c r="C43">
-        <v>-0.3430517714995615</v>
+        <v>2.072468163504899</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.5263835343881967</v>
+        <v>-1.523834393913832</v>
       </c>
       <c r="C44">
-        <v>0.81029268781492</v>
+        <v>1.528154129086003</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-1.031947456236597</v>
+        <v>0.351083820767002</v>
       </c>
       <c r="C45">
-        <v>0.6540077743542375</v>
+        <v>0.7096084291906593</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.9339395977487533</v>
+        <v>-0.7141320681515096</v>
       </c>
       <c r="C46">
-        <v>-0.7275960000981367</v>
+        <v>0.3302314576408448</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.3944577604220223</v>
+        <v>0.1229811198342183</v>
       </c>
       <c r="C47">
-        <v>1.397502826711331</v>
+        <v>-0.8855605635903143</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.8621036287506203</v>
+        <v>0.4749317911921787</v>
       </c>
       <c r="C48">
-        <v>-2.384381170053327</v>
+        <v>0.08071861231049127</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.4757090426738302</v>
+        <v>0.4800095280531043</v>
       </c>
       <c r="C49">
-        <v>-1.33287674080584</v>
+        <v>-0.489533411600525</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.3658394775998194</v>
+        <v>-0.2804820326403112</v>
       </c>
       <c r="C50">
-        <v>0.123064855567342</v>
+        <v>0.4575457585729107</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>2.409663724042644</v>
+        <v>0.1746415556987465</v>
       </c>
       <c r="C51">
-        <v>-0.1497135873889272</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>0.1550960867722146</v>
-      </c>
-      <c r="C52">
-        <v>0.9558123892971132</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-0.06063140809697429</v>
-      </c>
-      <c r="C53">
-        <v>-0.3551735407272315</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-0.6652742439825027</v>
-      </c>
-      <c r="C54">
-        <v>1.880448877402307</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>0.0949603499536566</v>
-      </c>
-      <c r="C55">
-        <v>-0.9159432875245388</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>0.3162412609217138</v>
-      </c>
-      <c r="C56">
-        <v>-2.573474362221215</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.3938577783855147</v>
-      </c>
-      <c r="C57">
-        <v>0.7034737411624773</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>0.4534581090991588</v>
-      </c>
-      <c r="C58">
-        <v>-0.8105230370044236</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>0.7085018267188483</v>
-      </c>
-      <c r="C59">
-        <v>0.2918975763925797</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>-0.816235388572651</v>
-      </c>
-      <c r="C60">
-        <v>-1.367716645363792</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>-1.974334546518878</v>
-      </c>
-      <c r="C61">
-        <v>-0.7892011635173563</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>-0.5681665556847608</v>
-      </c>
-      <c r="C62">
-        <v>0.2709047942743955</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>0.1051921200261315</v>
-      </c>
-      <c r="C63">
-        <v>1.471789341837131</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.3042454851469208</v>
-      </c>
-      <c r="C64">
-        <v>0.4996775222836906</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-1.892082242797957</v>
-      </c>
-      <c r="C65">
-        <v>-0.8171243828035581</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>1.057682003967577</v>
-      </c>
-      <c r="C66">
-        <v>-0.8270553825846357</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>0.7765670879686469</v>
-      </c>
-      <c r="C67">
-        <v>-2.14070366091218</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>-1.192603864827957</v>
-      </c>
-      <c r="C68">
-        <v>-1.581439789192015</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.3718631623984813</v>
-      </c>
-      <c r="C69">
-        <v>1.393138343627637</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-1.353877954197359</v>
-      </c>
-      <c r="C70">
-        <v>-0.07357469708109303</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>0.1285305914767727</v>
-      </c>
-      <c r="C71">
-        <v>0.279619096637416</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>0.7914625581728785</v>
-      </c>
-      <c r="C72">
-        <v>0.6072770582053086</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.2134792211921318</v>
-      </c>
-      <c r="C73">
-        <v>0.7140583282785822</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>0.4778455785823286</v>
-      </c>
-      <c r="C74">
-        <v>1.485729771304685</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-1.430830235538572</v>
-      </c>
-      <c r="C75">
-        <v>1.409248546588229</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>-0.2130578153397587</v>
-      </c>
-      <c r="C76">
-        <v>1.049399264039039</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>0.1714489847970959</v>
-      </c>
-      <c r="C77">
-        <v>-1.449914992716359</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-1.200930061090307</v>
-      </c>
-      <c r="C78">
-        <v>0.7094872009505202</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>-0.3404443898614166</v>
-      </c>
-      <c r="C79">
-        <v>0.3603988189425423</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>1.2168769815129</v>
-      </c>
-      <c r="C80">
-        <v>-2.525985207340757</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.8397795167153971</v>
-      </c>
-      <c r="C81">
-        <v>-1.142096552845263</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>-0.1764021038085073</v>
-      </c>
-      <c r="C82">
-        <v>1.278872113004385</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>0.5570273155150038</v>
-      </c>
-      <c r="C83">
-        <v>-1.456549122141743</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>-0.2793873289479581</v>
-      </c>
-      <c r="C84">
-        <v>0.8465797589679919</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>0.8252239111720397</v>
-      </c>
-      <c r="C85">
-        <v>-0.8695477097156609</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-1.657418720631642</v>
-      </c>
-      <c r="C86">
-        <v>-0.5523755321310837</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>1.587478818910108</v>
-      </c>
-      <c r="C87">
-        <v>-0.4457055838766129</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>0.2111609947389484</v>
-      </c>
-      <c r="C88">
-        <v>1.571833134868858</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-1.009185606984122</v>
-      </c>
-      <c r="C89">
-        <v>-1.140136689177669</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-0.1103126513855742</v>
-      </c>
-      <c r="C90">
-        <v>-1.492684015122098</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-1.393129726796572</v>
-      </c>
-      <c r="C91">
-        <v>-0.6172169515023471</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>-1.803144936831143</v>
-      </c>
-      <c r="C92">
-        <v>2.17893450164389</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>0.3087535154907825</v>
-      </c>
-      <c r="C93">
-        <v>-0.8490045215858026</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>1.572704509969112</v>
-      </c>
-      <c r="C94">
-        <v>0.1590736996567998</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>-0.6260104761485629</v>
-      </c>
-      <c r="C95">
-        <v>1.042711708153405</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-0.3177347623000683</v>
-      </c>
-      <c r="C96">
-        <v>0.9779721099135158</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>0.7055538016935646</v>
-      </c>
-      <c r="C97">
-        <v>0.2267600361311488</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>0.4489965238958525</v>
-      </c>
-      <c r="C98">
-        <v>1.021721571051203</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-0.1074318630423984</v>
-      </c>
-      <c r="C99">
-        <v>-0.3228587691300756</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-1.046900922621338</v>
-      </c>
-      <c r="C100">
-        <v>-0.2591039503893558</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>0.1017952611768533</v>
-      </c>
-      <c r="C101">
-        <v>-0.3984037637235489</v>
+        <v>-0.09116102200935179</v>
       </c>
     </row>
   </sheetData>
